--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,15 +434,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -460,22 +470,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.8681</v>
+        <v>17.68722</v>
       </c>
       <c r="D2" t="n">
-        <v>17.58853</v>
+        <v>17.18788</v>
       </c>
       <c r="E2" t="n">
-        <v>17.74429</v>
+        <v>17.44493</v>
       </c>
       <c r="F2" t="n">
-        <v>45.24554</v>
+        <v>58.59247</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05445</v>
+        <v>44.93129</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9275</v>
+        <v>90.72566999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.05392</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.88565</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +501,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.0131</v>
+        <v>18.02652</v>
       </c>
       <c r="D3" t="n">
-        <v>17.66988</v>
+        <v>17.2949</v>
       </c>
       <c r="E3" t="n">
-        <v>17.67243</v>
+        <v>17.79158</v>
       </c>
       <c r="F3" t="n">
-        <v>45.8096</v>
+        <v>58.92252</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05405</v>
+        <v>43.76145</v>
       </c>
       <c r="H3" t="n">
-        <v>1.91846</v>
+        <v>89.67475</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05386</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.92015</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +532,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.63788</v>
+        <v>17.84684</v>
       </c>
       <c r="D4" t="n">
-        <v>17.61485</v>
+        <v>17.15976</v>
       </c>
       <c r="E4" t="n">
-        <v>17.52868</v>
+        <v>17.70967</v>
       </c>
       <c r="F4" t="n">
-        <v>44.67249</v>
+        <v>58.22095</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0541</v>
+        <v>44.54304</v>
       </c>
       <c r="H4" t="n">
-        <v>1.94001</v>
+        <v>90.16104</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05383</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.93479</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +563,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.81655</v>
+        <v>18.11199</v>
       </c>
       <c r="D5" t="n">
-        <v>17.79573</v>
+        <v>17.42369</v>
       </c>
       <c r="E5" t="n">
-        <v>17.80573</v>
+        <v>17.435</v>
       </c>
       <c r="F5" t="n">
-        <v>45.65883</v>
+        <v>57.98111</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05338</v>
+        <v>45.72495</v>
       </c>
       <c r="H5" t="n">
-        <v>1.95375</v>
+        <v>91.86322</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05409</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.93623</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +594,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.68956</v>
+        <v>17.58348</v>
       </c>
       <c r="D6" t="n">
-        <v>17.61943</v>
+        <v>17.46257</v>
       </c>
       <c r="E6" t="n">
-        <v>17.44244</v>
+        <v>17.48411</v>
       </c>
       <c r="F6" t="n">
-        <v>45.5238</v>
+        <v>59.24049</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05367</v>
+        <v>45.13136</v>
       </c>
       <c r="H6" t="n">
-        <v>1.95427</v>
+        <v>90.60531</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05415</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.93833</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +625,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.77828</v>
+        <v>17.93848</v>
       </c>
       <c r="D7" t="n">
-        <v>17.38177</v>
+        <v>17.4235</v>
       </c>
       <c r="E7" t="n">
-        <v>17.70634</v>
+        <v>17.6695</v>
       </c>
       <c r="F7" t="n">
-        <v>44.7351</v>
+        <v>59.86586</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05505</v>
+        <v>45.49163</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9892</v>
+        <v>90.39046999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.05427</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.94253</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +656,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.85955</v>
+        <v>17.73935</v>
       </c>
       <c r="D8" t="n">
-        <v>17.51793</v>
+        <v>17.50425</v>
       </c>
       <c r="E8" t="n">
-        <v>17.81656</v>
+        <v>17.51563</v>
       </c>
       <c r="F8" t="n">
-        <v>44.82104</v>
+        <v>58.977</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05368</v>
+        <v>44.94374</v>
       </c>
       <c r="H8" t="n">
-        <v>1.89508</v>
+        <v>89.78576</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05383</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.88545</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +687,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.91392</v>
+        <v>18.07061</v>
       </c>
       <c r="D9" t="n">
-        <v>17.74537</v>
+        <v>17.36777</v>
       </c>
       <c r="E9" t="n">
-        <v>17.81431</v>
+        <v>17.51968</v>
       </c>
       <c r="F9" t="n">
-        <v>45.25009</v>
+        <v>57.20827</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05484</v>
+        <v>44.80643</v>
       </c>
       <c r="H9" t="n">
-        <v>1.92829</v>
+        <v>88.35953000000001</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.05288</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.96154</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +718,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.66945</v>
+        <v>17.4837</v>
       </c>
       <c r="D10" t="n">
-        <v>17.86509</v>
+        <v>17.19005</v>
       </c>
       <c r="E10" t="n">
-        <v>17.51598</v>
+        <v>17.41936</v>
       </c>
       <c r="F10" t="n">
-        <v>46.00231</v>
+        <v>59.05102</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05369</v>
+        <v>44.44172</v>
       </c>
       <c r="H10" t="n">
-        <v>1.93809</v>
+        <v>90.44911</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05434</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.95151</v>
       </c>
     </row>
     <row r="11">
@@ -696,12 +760,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -713,8 +792,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
-        </is>
+          <t>Pad 2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>17.72814</v>
+      </c>
+      <c r="D12" t="n">
+        <v>17.67337</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.68244</v>
+      </c>
+      <c r="F12" t="n">
+        <v>58.39883</v>
+      </c>
+      <c r="G12" t="n">
+        <v>43.97155</v>
+      </c>
+      <c r="H12" t="n">
+        <v>90.65864999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05345</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.93515</v>
       </c>
     </row>
     <row r="13">
@@ -723,6 +826,30 @@
           <t>Unit 8</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>17.85655</v>
+      </c>
+      <c r="D13" t="n">
+        <v>17.45021</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.57046</v>
+      </c>
+      <c r="F13" t="n">
+        <v>59.62286</v>
+      </c>
+      <c r="G13" t="n">
+        <v>45.39254</v>
+      </c>
+      <c r="H13" t="n">
+        <v>90.86147</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.05434</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.91892</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -730,6 +857,30 @@
           <t>Unit 9</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>18.22539</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17.59378</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.71264</v>
+      </c>
+      <c r="F14" t="n">
+        <v>58.94222</v>
+      </c>
+      <c r="G14" t="n">
+        <v>44.71738</v>
+      </c>
+      <c r="H14" t="n">
+        <v>90.12307</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05303</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.92995</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -737,6 +888,30 @@
           <t>Unit 4</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>18.03527</v>
+      </c>
+      <c r="D15" t="n">
+        <v>17.57873</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.708</v>
+      </c>
+      <c r="F15" t="n">
+        <v>57.85906</v>
+      </c>
+      <c r="G15" t="n">
+        <v>45.28019</v>
+      </c>
+      <c r="H15" t="n">
+        <v>90.04868</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.91916</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -744,6 +919,30 @@
           <t>Unit 5</t>
         </is>
       </c>
+      <c r="C16" t="n">
+        <v>17.91101</v>
+      </c>
+      <c r="D16" t="n">
+        <v>17.63628</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.70686</v>
+      </c>
+      <c r="F16" t="n">
+        <v>58.36399</v>
+      </c>
+      <c r="G16" t="n">
+        <v>44.32624</v>
+      </c>
+      <c r="H16" t="n">
+        <v>89.02361000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.05395</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.92966</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -751,6 +950,30 @@
           <t>Unit 6</t>
         </is>
       </c>
+      <c r="C17" t="n">
+        <v>17.75077</v>
+      </c>
+      <c r="D17" t="n">
+        <v>17.47827</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.70151</v>
+      </c>
+      <c r="F17" t="n">
+        <v>59.36692</v>
+      </c>
+      <c r="G17" t="n">
+        <v>44.37154</v>
+      </c>
+      <c r="H17" t="n">
+        <v>91.75466</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05307</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.93399</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -758,6 +981,30 @@
           <t>Unit 1</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>18.16396</v>
+      </c>
+      <c r="D18" t="n">
+        <v>17.72041</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.80676</v>
+      </c>
+      <c r="F18" t="n">
+        <v>58.30012</v>
+      </c>
+      <c r="G18" t="n">
+        <v>44.68994</v>
+      </c>
+      <c r="H18" t="n">
+        <v>91.58532</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.05375</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.96183</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -765,6 +1012,30 @@
           <t>Unit 2</t>
         </is>
       </c>
+      <c r="C19" t="n">
+        <v>18.11327</v>
+      </c>
+      <c r="D19" t="n">
+        <v>17.50172</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.75544</v>
+      </c>
+      <c r="F19" t="n">
+        <v>57.89876</v>
+      </c>
+      <c r="G19" t="n">
+        <v>44.56903</v>
+      </c>
+      <c r="H19" t="n">
+        <v>90.05516</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.05269</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.90485</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -772,46 +1043,55 @@
           <t>Unit 3</t>
         </is>
       </c>
+      <c r="C20" t="n">
+        <v>17.97718</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17.40755</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.69739</v>
+      </c>
+      <c r="F20" t="n">
+        <v>58.88123</v>
+      </c>
+      <c r="G20" t="n">
+        <v>44.61057</v>
+      </c>
+      <c r="H20" t="n">
+        <v>88.75077</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.05387</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.94028</v>
+      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -823,32 +1103,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.79011</v>
+        <v>17.65012</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08575000000000001</v>
+        <v>16.61078</v>
       </c>
       <c r="E22" t="n">
-        <v>0.63507</v>
+        <v>17.05869</v>
       </c>
       <c r="F22" t="n">
-        <v>1.01266</v>
+        <v>23.1036</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1175</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.008019999999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.10071</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.13188</v>
+        <v>36.65659</v>
       </c>
     </row>
     <row r="23">
@@ -858,28 +1129,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.8015600000000001</v>
+        <v>17.46664</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08638</v>
+        <v>16.78232</v>
       </c>
       <c r="E23" t="n">
-        <v>0.63273</v>
+        <v>17.18263</v>
       </c>
       <c r="F23" t="n">
-        <v>1.02903</v>
+        <v>22.78786</v>
       </c>
       <c r="G23" t="n">
-        <v>0.11548</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.008030000000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09916999999999999</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.13504</v>
+        <v>36.00091</v>
       </c>
     </row>
     <row r="24">
@@ -889,28 +1151,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.79544</v>
+        <v>17.81506</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08619</v>
+        <v>16.88072</v>
       </c>
       <c r="E24" t="n">
-        <v>0.65169</v>
+        <v>17.26845</v>
       </c>
       <c r="F24" t="n">
-        <v>1.02826</v>
+        <v>23.02813</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1149</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.007979999999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.0973</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.1362</v>
+        <v>36.3749</v>
       </c>
     </row>
     <row r="25">
@@ -920,28 +1173,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.78753</v>
+        <v>17.86932</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08526</v>
+        <v>17.14074</v>
       </c>
       <c r="E25" t="n">
-        <v>0.65357</v>
+        <v>17.14279</v>
       </c>
       <c r="F25" t="n">
-        <v>1.02565</v>
+        <v>23.636</v>
       </c>
       <c r="G25" t="n">
-        <v>0.11929</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00808</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09844</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.13579</v>
+        <v>35.71699</v>
       </c>
     </row>
     <row r="26">
@@ -951,28 +1195,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.81366</v>
+        <v>17.80384</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0838</v>
+        <v>16.69701</v>
       </c>
       <c r="E26" t="n">
-        <v>0.63567</v>
+        <v>17.64353</v>
       </c>
       <c r="F26" t="n">
-        <v>1.01525</v>
+        <v>22.90105</v>
       </c>
       <c r="G26" t="n">
-        <v>0.11753</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00814</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09986</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.13441</v>
+        <v>36.04521</v>
       </c>
     </row>
     <row r="27">
@@ -982,28 +1217,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.79278</v>
+        <v>17.8717</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08455</v>
+        <v>16.86606</v>
       </c>
       <c r="E27" t="n">
-        <v>0.62769</v>
+        <v>17.61783</v>
       </c>
       <c r="F27" t="n">
-        <v>1.05101</v>
+        <v>23.26794</v>
       </c>
       <c r="G27" t="n">
-        <v>0.11621</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.008229999999999999</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09796000000000001</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.13468</v>
+        <v>36.03134</v>
       </c>
     </row>
     <row r="28">
@@ -1013,28 +1239,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.80352</v>
+        <v>17.4774</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08661000000000001</v>
+        <v>16.80843</v>
       </c>
       <c r="E28" t="n">
-        <v>0.65949</v>
+        <v>17.09462</v>
       </c>
       <c r="F28" t="n">
-        <v>1.03893</v>
+        <v>23.26226</v>
       </c>
       <c r="G28" t="n">
-        <v>0.11311</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00812</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09879</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.13167</v>
+        <v>35.30142</v>
       </c>
     </row>
     <row r="29">
@@ -1044,28 +1261,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.81265</v>
+        <v>17.63458</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08672000000000001</v>
+        <v>17.00124</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6523099999999999</v>
+        <v>17.50467</v>
       </c>
       <c r="F29" t="n">
-        <v>1.02247</v>
+        <v>22.70473</v>
       </c>
       <c r="G29" t="n">
-        <v>0.11395</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.008059999999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09801</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.13441</v>
+        <v>36.59555</v>
       </c>
     </row>
     <row r="30">
@@ -1075,28 +1283,345 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.78922</v>
+        <v>17.74389</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08731</v>
+        <v>17.35907</v>
       </c>
       <c r="E30" t="n">
-        <v>0.64515</v>
+        <v>17.43128</v>
       </c>
       <c r="F30" t="n">
-        <v>1.04261</v>
+        <v>22.90997</v>
       </c>
       <c r="G30" t="n">
-        <v>0.11566</v>
-      </c>
-      <c r="H30" t="n">
+        <v>35.79574</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.77946</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0859</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.64753</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.02656</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.11458</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.007939999999999999</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09987</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.13228</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.79926</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08684</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.64575</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.01919</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.11471</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09857</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.13376</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.80582</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08513</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.63432</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.03445</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.11558</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00805</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09902</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.13641</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.77343</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08552</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.65227</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.00235</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.11706</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.008109999999999999</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09895</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.13387</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.79421</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08753</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.64374</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.02312</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.11636</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.008059999999999999</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09981</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.13221</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.79528</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08601</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.64389</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.01831</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.11737</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09718</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.13159</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.78201</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08559</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.63509</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.03851</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.11618</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.008109999999999999</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.13442</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08502</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.65491</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.01952</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.11583</v>
+      </c>
+      <c r="H39" t="n">
         <v>0.00793</v>
       </c>
-      <c r="I30" t="n">
-        <v>0.09846000000000001</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.13255</v>
+      <c r="I39" t="n">
+        <v>0.0994</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.13636</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.80171</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08518000000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6407</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.02203</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.11542</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.10006</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.13281</v>
       </c>
     </row>
   </sheetData>
